--- a/2026/GALERIA MITRE/ABRIL/Abril MITRE.xlsx
+++ b/2026/GALERIA MITRE/ABRIL/Abril MITRE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GALERIA MITRE\ABRIL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GALERIA MITRE\ABRIL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD123BB-7C36-43C4-9949-3591575C933C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66983D1-E87E-430C-9232-6A9A0A8B1E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$D$116</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="184">
   <si>
     <t>TOTAL SUELDO</t>
   </si>
@@ -565,6 +560,24 @@
   </si>
   <si>
     <t>Dinero Fondo FIMA - Al 07/05/2026</t>
+  </si>
+  <si>
+    <t>Anotacion:</t>
+  </si>
+  <si>
+    <t>UF:</t>
+  </si>
+  <si>
+    <t>Dicen que depositaron $273,000 el 15/04 y no se lo computamos</t>
+  </si>
+  <si>
+    <t>El deposito no identificado de $50.000 es de el</t>
+  </si>
+  <si>
+    <t>10 y 16</t>
+  </si>
+  <si>
+    <t>Nelida Micaela atanes es local 10 y 16. El deposito no identificado del mes anterior es del local 10. Este mes abono de mas.</t>
   </si>
 </sst>
 </file>
@@ -768,7 +781,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -835,6 +848,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1195,7 +1220,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1374,12 +1399,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1398,7 +1421,7 @@
     <xf numFmtId="8" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1407,47 +1430,128 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1461,74 +1565,66 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="7" fillId="9" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -1597,9 +1693,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1637,9 +1733,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1672,26 +1768,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1724,26 +1803,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1918,20 +1980,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L116"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="102" t="s">
         <v>64</v>
       </c>
@@ -1939,7 +2001,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="98" t="s">
         <v>128</v>
       </c>
@@ -1947,7 +2009,7 @@
       <c r="C2" s="98"/>
       <c r="D2" s="98"/>
     </row>
-    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="98" t="s">
         <v>71</v>
       </c>
@@ -1955,76 +2017,76 @@
       <c r="C3" s="98"/>
       <c r="D3" s="98"/>
     </row>
-    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="155" t="s">
+    <row r="4" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="162" t="s">
         <v>173</v>
       </c>
-      <c r="B4" s="155"/>
+      <c r="B4" s="162"/>
       <c r="C4" s="99"/>
       <c r="D4" s="99"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="155"/>
-      <c r="B5" s="155"/>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="162"/>
+      <c r="B5" s="162"/>
       <c r="C5" s="99"/>
       <c r="D5" s="99"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="155"/>
-      <c r="B6" s="155"/>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="162"/>
+      <c r="B6" s="162"/>
       <c r="C6" s="99"/>
       <c r="D6" s="99"/>
     </row>
-    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="155"/>
-      <c r="B7" s="155"/>
+    <row r="7" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="162"/>
+      <c r="B7" s="162"/>
       <c r="C7" s="99"/>
       <c r="D7" s="99"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B9" s="152" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="175" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B10" s="152"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="152"/>
-    </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="175"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="175"/>
+    </row>
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="162" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="155"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="155"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="155"/>
-      <c r="B15" s="155"/>
-      <c r="C15" s="155"/>
-      <c r="D15" s="155"/>
-    </row>
-    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155"/>
-      <c r="B16" s="155"/>
-      <c r="C16" s="155"/>
-      <c r="D16" s="155"/>
-    </row>
-    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="155"/>
-      <c r="D17" s="155"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="162"/>
+      <c r="C14" s="162"/>
+      <c r="D14" s="162"/>
+    </row>
+    <row r="15" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="162"/>
+      <c r="B15" s="162"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="162"/>
+    </row>
+    <row r="16" spans="1:4" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="162"/>
+      <c r="B16" s="162"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="162"/>
+    </row>
+    <row r="17" spans="1:7" ht="156.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="162"/>
+      <c r="B17" s="162"/>
+      <c r="C17" s="162"/>
+      <c r="D17" s="162"/>
+    </row>
+    <row r="18" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>26</v>
       </c>
@@ -2032,7 +2094,7 @@
       <c r="C21" s="8"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="25" t="s">
         <v>52</v>
       </c>
@@ -2040,11 +2102,11 @@
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
     </row>
-    <row r="23" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="150" t="s">
+    <row r="23" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="172" t="s">
         <v>146</v>
       </c>
-      <c r="B23" s="151"/>
+      <c r="B23" s="173"/>
       <c r="C23" s="113">
         <v>560501.56999999995</v>
       </c>
@@ -2052,7 +2114,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>55</v>
       </c>
@@ -2060,7 +2122,7 @@
       <c r="C24" s="113"/>
       <c r="D24" s="69"/>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
@@ -2069,13 +2131,13 @@
       <c r="D25" s="69"/>
       <c r="G25" s="125"/>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="113"/>
       <c r="D26" s="69"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="43" t="s">
         <v>53</v>
       </c>
@@ -2086,11 +2148,11 @@
       </c>
       <c r="D27" s="43"/>
     </row>
-    <row r="28" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="150" t="s">
+    <row r="28" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="172" t="s">
         <v>147</v>
       </c>
-      <c r="B28" s="151"/>
+      <c r="B28" s="173"/>
       <c r="C28" s="113">
         <v>582828.23</v>
       </c>
@@ -2098,7 +2160,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="113">
@@ -2106,7 +2168,7 @@
       </c>
       <c r="D29" s="101"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="113">
@@ -2114,13 +2176,13 @@
       </c>
       <c r="D30" s="101"/>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="128"/>
       <c r="D31" s="101"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
         <v>53</v>
       </c>
@@ -2131,11 +2193,11 @@
       </c>
       <c r="D32" s="70"/>
     </row>
-    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="161" t="s">
+    <row r="33" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="170" t="s">
         <v>130</v>
       </c>
-      <c r="B33" s="162"/>
+      <c r="B33" s="171"/>
       <c r="C33" s="113">
         <v>1688447.15</v>
       </c>
@@ -2143,7 +2205,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="113">
@@ -2151,7 +2213,7 @@
       </c>
       <c r="D34" s="101"/>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="113">
@@ -2159,13 +2221,13 @@
       </c>
       <c r="D35" s="101"/>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="128"/>
       <c r="D36" s="101"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>53</v>
       </c>
@@ -2177,7 +2239,7 @@
       <c r="D37" s="70"/>
       <c r="F37" s="13"/>
     </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="17" t="s">
         <v>0</v>
       </c>
@@ -2190,7 +2252,7 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>38</v>
       </c>
@@ -2199,7 +2261,7 @@
       <c r="D39" s="72"/>
       <c r="F39" s="13"/>
     </row>
-    <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="103" t="s">
         <v>174</v>
       </c>
@@ -2208,7 +2270,7 @@
       <c r="D40" s="111"/>
       <c r="G40" s="13"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="17" t="s">
         <v>34</v>
       </c>
@@ -2219,7 +2281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="23" t="s">
         <v>49</v>
       </c>
@@ -2227,11 +2289,11 @@
       <c r="C42" s="27"/>
       <c r="D42" s="49"/>
     </row>
-    <row r="43" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="153" t="s">
+    <row r="43" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="B43" s="154"/>
+      <c r="B43" s="167"/>
       <c r="C43" s="127">
         <v>111379</v>
       </c>
@@ -2239,11 +2301,11 @@
         <v>129</v>
       </c>
     </row>
-    <row r="44" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="153" t="s">
+    <row r="44" spans="1:7" s="32" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="B44" s="154"/>
+      <c r="B44" s="167"/>
       <c r="C44" s="127">
         <v>111379</v>
       </c>
@@ -2251,7 +2313,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="24" t="s">
         <v>1</v>
       </c>
@@ -2262,7 +2324,7 @@
         <v>222758</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="23" t="s">
         <v>35</v>
       </c>
@@ -2270,7 +2332,7 @@
       <c r="C46" s="30"/>
       <c r="D46" s="74"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="69" t="s">
         <v>65</v>
       </c>
@@ -2283,11 +2345,11 @@
       </c>
       <c r="F47" s="104"/>
     </row>
-    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="153" t="s">
+    <row r="48" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="166" t="s">
         <v>139</v>
       </c>
-      <c r="B48" s="154"/>
+      <c r="B48" s="167"/>
       <c r="C48" s="131">
         <v>11596.99</v>
       </c>
@@ -2296,11 +2358,11 @@
       </c>
       <c r="F48" s="104"/>
     </row>
-    <row r="49" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="153" t="s">
+    <row r="49" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="166" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="154"/>
+      <c r="B49" s="167"/>
       <c r="C49" s="131">
         <v>11596.99</v>
       </c>
@@ -2309,7 +2371,7 @@
       </c>
       <c r="F49" s="104"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="69" t="s">
         <v>66</v>
       </c>
@@ -2321,7 +2383,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="69" t="s">
         <v>67</v>
       </c>
@@ -2334,7 +2396,7 @@
         <v>Debito 13/04</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="69" t="s">
         <v>68</v>
       </c>
@@ -2347,7 +2409,7 @@
         <v>Debito 13/04</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="24" t="s">
         <v>2</v>
       </c>
@@ -2358,7 +2420,7 @@
         <v>781794.14999999991</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="23" t="s">
         <v>37</v>
       </c>
@@ -2366,7 +2428,7 @@
       <c r="C54" s="30"/>
       <c r="D54" s="74"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="69" t="s">
         <v>135</v>
       </c>
@@ -2378,7 +2440,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="69" t="s">
         <v>134</v>
       </c>
@@ -2390,7 +2452,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="69" t="s">
         <v>136</v>
       </c>
@@ -2402,13 +2464,13 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="69"/>
       <c r="B58" s="132"/>
       <c r="C58" s="116"/>
       <c r="D58" s="107"/>
     </row>
-    <row r="59" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="24" t="s">
         <v>3</v>
       </c>
@@ -2419,7 +2481,7 @@
         <v>530406.55999999994</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="23" t="s">
         <v>36</v>
       </c>
@@ -2427,11 +2489,11 @@
       <c r="C60" s="29"/>
       <c r="D60" s="76"/>
     </row>
-    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="159" t="s">
+    <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="168" t="s">
         <v>132</v>
       </c>
-      <c r="B61" s="160"/>
+      <c r="B61" s="169"/>
       <c r="C61" s="116">
         <v>300000</v>
       </c>
@@ -2439,11 +2501,11 @@
         <v>131</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="153" t="s">
+    <row r="62" spans="1:6" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="166" t="s">
         <v>143</v>
       </c>
-      <c r="B62" s="154"/>
+      <c r="B62" s="167"/>
       <c r="C62" s="116">
         <v>230000</v>
       </c>
@@ -2453,11 +2515,11 @@
       <c r="E62" s="116"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="153" t="s">
+    <row r="63" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="166" t="s">
         <v>144</v>
       </c>
-      <c r="B63" s="154"/>
+      <c r="B63" s="167"/>
       <c r="C63" s="116">
         <v>95000</v>
       </c>
@@ -2467,15 +2529,15 @@
       <c r="E63" s="116"/>
       <c r="F63" s="37"/>
     </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="159"/>
-      <c r="B64" s="160"/>
+    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="168"/>
+      <c r="B64" s="169"/>
       <c r="C64" s="116"/>
       <c r="D64" s="109"/>
       <c r="E64" s="37"/>
       <c r="F64" s="37"/>
     </row>
-    <row r="65" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="24" t="s">
         <v>11</v>
       </c>
@@ -2486,7 +2548,7 @@
         <v>625000</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="23" t="s">
         <v>29</v>
       </c>
@@ -2494,17 +2556,17 @@
       <c r="C66" s="18"/>
       <c r="D66" s="76"/>
     </row>
-    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="153" t="s">
+    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="166" t="s">
         <v>76</v>
       </c>
-      <c r="B67" s="154"/>
+      <c r="B67" s="167"/>
       <c r="C67" s="116">
         <v>60000</v>
       </c>
       <c r="D67" s="80"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="69" t="s">
         <v>72</v>
       </c>
@@ -2515,7 +2577,7 @@
       </c>
       <c r="D68" s="78"/>
     </row>
-    <row r="69" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="42" t="s">
         <v>34</v>
       </c>
@@ -2526,27 +2588,27 @@
         <v>153428.22999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="69"/>
       <c r="D70" s="82"/>
     </row>
-    <row r="71" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="156" t="s">
+    <row r="71" spans="1:6" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="B71" s="157"/>
-      <c r="C71" s="158"/>
+      <c r="B71" s="164"/>
+      <c r="C71" s="165"/>
       <c r="D71" s="83"/>
     </row>
-    <row r="72" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1"/>
       <c r="C72" s="84"/>
       <c r="D72" s="85"/>
       <c r="E72" s="37"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>30</v>
       </c>
@@ -2559,16 +2621,16 @@
       <c r="E73" s="37"/>
       <c r="F73" s="37"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C74" s="84"/>
       <c r="D74" s="84"/>
       <c r="F74" s="105"/>
     </row>
-    <row r="75" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C75" s="84"/>
       <c r="D75" s="84"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="10" t="s">
         <v>39</v>
       </c>
@@ -2576,25 +2638,25 @@
       <c r="C76" s="88"/>
       <c r="D76" s="89"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="150"/>
-      <c r="B77" s="151"/>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="172"/>
+      <c r="B77" s="173"/>
       <c r="C77" s="77"/>
       <c r="D77" s="75"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="150"/>
-      <c r="B78" s="151"/>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="172"/>
+      <c r="B78" s="173"/>
       <c r="C78" s="77"/>
       <c r="D78" s="75"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="92"/>
       <c r="B79" s="93"/>
       <c r="C79" s="77"/>
       <c r="D79" s="75"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="40"/>
       <c r="B80" s="39"/>
       <c r="C80" s="45"/>
@@ -2603,9 +2665,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="19" t="s">
         <v>40</v>
       </c>
@@ -2615,8 +2677,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="85" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
         <v>41</v>
       </c>
@@ -2627,8 +2689,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="87" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="67" t="s">
         <v>31</v>
       </c>
@@ -2638,7 +2700,7 @@
       </c>
       <c r="C87" s="37"/>
     </row>
-    <row r="88" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="67" t="s">
         <v>32</v>
       </c>
@@ -2647,7 +2709,7 @@
         <v>5145163.8899999987</v>
       </c>
     </row>
-    <row r="89" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="67" t="s">
         <v>42</v>
       </c>
@@ -2656,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="67" t="s">
         <v>59</v>
       </c>
@@ -2665,13 +2727,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="s">
         <v>51</v>
       </c>
       <c r="B94" s="34"/>
     </row>
-    <row r="95" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="22" t="s">
         <v>33</v>
       </c>
@@ -2679,7 +2741,7 @@
         <v>4038909.89</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="15" t="s">
         <v>62</v>
       </c>
@@ -2688,7 +2750,7 @@
         <v>2804769.5600000005</v>
       </c>
     </row>
-    <row r="97" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="133" t="s">
         <v>61</v>
       </c>
@@ -2697,7 +2759,7 @@
         <v>391723</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="16" t="s">
         <v>75</v>
       </c>
@@ -2705,7 +2767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="33" t="s">
         <v>43</v>
       </c>
@@ -2714,7 +2776,7 @@
         <v>-5145163.8899999987</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="16" t="s">
         <v>44</v>
       </c>
@@ -2723,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="21" t="s">
         <v>11</v>
       </c>
@@ -2733,49 +2795,49 @@
       </c>
       <c r="D101" s="129"/>
     </row>
-    <row r="102" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="134"/>
-      <c r="B102" s="135"/>
+    <row r="102" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="2"/>
+      <c r="B102" s="134"/>
       <c r="D102" s="129"/>
     </row>
-    <row r="103" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="189" t="s">
+    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="147" t="s">
         <v>177</v>
       </c>
-      <c r="B103" s="190">
+      <c r="B103" s="148">
         <v>1331900.92</v>
       </c>
       <c r="D103" s="129"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="134"/>
-      <c r="B104" s="135"/>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" s="2"/>
+      <c r="B104" s="134"/>
       <c r="D104" s="129"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="134"/>
-      <c r="B105" s="135"/>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" s="2"/>
+      <c r="B105" s="134"/>
       <c r="D105" s="129"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="134"/>
-      <c r="B106" s="135"/>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" s="2"/>
+      <c r="B106" s="134"/>
       <c r="D106" s="129"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D107" s="130"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="149" t="s">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="174" t="s">
         <v>50</v>
       </c>
-      <c r="B108" s="149"/>
-    </row>
-    <row r="109" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="149"/>
-      <c r="B109" s="149"/>
-    </row>
-    <row r="110" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="174"/>
+    </row>
+    <row r="109" spans="1:4" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="174"/>
+      <c r="B109" s="174"/>
+    </row>
+    <row r="110" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="90" t="s">
         <v>162</v>
       </c>
@@ -2783,7 +2845,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="90" t="s">
         <v>168</v>
       </c>
@@ -2791,7 +2853,7 @@
         <v>64500</v>
       </c>
     </row>
-    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="90" t="s">
         <v>172</v>
       </c>
@@ -2799,7 +2861,7 @@
         <v>210000</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="90" t="s">
         <v>171</v>
       </c>
@@ -2807,7 +2869,7 @@
         <v>46400</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="90" t="s">
         <v>164</v>
       </c>
@@ -2815,7 +2877,7 @@
         <v>20823</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="38" t="s">
         <v>11</v>
       </c>
@@ -2824,11 +2886,16 @@
         <v>391723</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L116" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A108:B109"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="A43:B43"/>
     <mergeCell ref="A4:B7"/>
     <mergeCell ref="A14:D17"/>
     <mergeCell ref="A71:C71"/>
@@ -2843,11 +2910,6 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A108:B109"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2858,161 +2920,161 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="5.44140625" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="5.109375" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="7.5703125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" customWidth="1"/>
-    <col min="16" max="16" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.44140625" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="14.109375" customWidth="1"/>
+    <col min="16" max="16" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
-      <c r="B1" s="169" t="s">
+      <c r="B1" s="176" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="171"/>
-      <c r="K1" s="145" t="s">
+      <c r="C1" s="177"/>
+      <c r="D1" s="177"/>
+      <c r="E1" s="177"/>
+      <c r="F1" s="177"/>
+      <c r="G1" s="177"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="177"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="142">
+      <c r="L1" s="144"/>
+      <c r="M1" s="144"/>
+      <c r="N1" s="140">
         <v>5145163.8899999987</v>
       </c>
-      <c r="O1" s="143"/>
+      <c r="O1" s="141"/>
       <c r="P1" s="13"/>
     </row>
-    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6"/>
-      <c r="B2" s="172"/>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="173"/>
-      <c r="F2" s="173"/>
-      <c r="G2" s="173"/>
-      <c r="H2" s="173"/>
-      <c r="I2" s="173"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="147" t="s">
+      <c r="B2" s="179"/>
+      <c r="C2" s="180"/>
+      <c r="D2" s="180"/>
+      <c r="E2" s="180"/>
+      <c r="F2" s="180"/>
+      <c r="G2" s="180"/>
+      <c r="H2" s="180"/>
+      <c r="I2" s="180"/>
+      <c r="J2" s="181"/>
+      <c r="K2" s="145" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
       <c r="N2" s="114">
         <v>0</v>
       </c>
-      <c r="O2" s="144"/>
-    </row>
-    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="O2" s="142"/>
+    </row>
+    <row r="3" spans="1:18" ht="137.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6"/>
-      <c r="B3" s="186" t="s">
+      <c r="B3" s="195" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="187"/>
-      <c r="D3" s="187"/>
-      <c r="E3" s="187"/>
-      <c r="F3" s="187"/>
-      <c r="G3" s="187"/>
-      <c r="H3" s="187"/>
-      <c r="I3" s="187"/>
-      <c r="J3" s="187"/>
-      <c r="K3" s="187"/>
-      <c r="L3" s="187"/>
-      <c r="M3" s="187"/>
-      <c r="N3" s="187"/>
-      <c r="O3" s="188"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="163" t="s">
+      <c r="C3" s="196"/>
+      <c r="D3" s="196"/>
+      <c r="E3" s="196"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="196"/>
+      <c r="O3" s="197"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="165" t="s">
+      <c r="B4" s="200" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="C4" s="185" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="167" t="s">
+      <c r="D4" s="185" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="167" t="s">
+      <c r="E4" s="185" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="167" t="s">
+      <c r="F4" s="185" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="167" t="s">
+      <c r="G4" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="H4" s="185" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="181" t="s">
+      <c r="I4" s="190" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="179" t="s">
+      <c r="J4" s="187" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="179" t="s">
+      <c r="K4" s="187" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="179" t="s">
+      <c r="L4" s="187" t="s">
         <v>45</v>
       </c>
-      <c r="M4" s="184" t="s">
+      <c r="M4" s="193" t="s">
         <v>58</v>
       </c>
       <c r="N4" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="O4" s="175" t="s">
+      <c r="O4" s="182" t="s">
         <v>56</v>
       </c>
       <c r="R4" s="37"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="164"/>
-      <c r="B5" s="166"/>
-      <c r="C5" s="168"/>
-      <c r="D5" s="168"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="168"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="178"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="183"/>
-      <c r="L5" s="180"/>
-      <c r="M5" s="185"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="199"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="189"/>
+      <c r="D5" s="189"/>
+      <c r="E5" s="189"/>
+      <c r="F5" s="189"/>
+      <c r="G5" s="189"/>
+      <c r="H5" s="186"/>
+      <c r="I5" s="191"/>
+      <c r="J5" s="188"/>
+      <c r="K5" s="192"/>
+      <c r="L5" s="188"/>
+      <c r="M5" s="194"/>
       <c r="N5" s="46" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="O5" s="176"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="183"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>12</v>
       </c>
@@ -3066,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="48">
         <v>1</v>
@@ -3119,7 +3181,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>13</v>
       </c>
@@ -3176,7 +3238,7 @@
       </c>
       <c r="Q8" s="37"/>
     </row>
-    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>13</v>
       </c>
@@ -3187,7 +3249,7 @@
       <c r="C9" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="136" t="s">
+      <c r="D9" s="135" t="s">
         <v>80</v>
       </c>
       <c r="E9" s="119">
@@ -3233,7 +3295,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>14</v>
       </c>
@@ -3294,7 +3356,7 @@
       </c>
       <c r="R10" s="37"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>14</v>
       </c>
@@ -3351,7 +3413,7 @@
       </c>
       <c r="R11" s="37"/>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="118">
         <f t="shared" si="6"/>
@@ -3407,7 +3469,7 @@
       </c>
       <c r="R12" s="37"/>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="118">
         <f t="shared" si="6"/>
@@ -3466,7 +3528,7 @@
       </c>
       <c r="R13" s="37"/>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="118">
         <f t="shared" si="6"/>
@@ -3521,16 +3583,16 @@
       </c>
       <c r="R14" s="37"/>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="118">
+      <c r="B15" s="149">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="149" t="s">
         <v>114</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="149" t="s">
         <v>85</v>
       </c>
       <c r="E15" s="51">
@@ -3576,16 +3638,16 @@
       </c>
       <c r="R15" s="37"/>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
-      <c r="B16" s="118">
+      <c r="B16" s="224">
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="224" t="s">
         <v>115</v>
       </c>
-      <c r="D16" s="48" t="s">
+      <c r="D16" s="224" t="s">
         <v>86</v>
       </c>
       <c r="E16" s="51">
@@ -3629,9 +3691,12 @@
         <f t="shared" si="7"/>
         <v>9.9999999999999992E-2</v>
       </c>
+      <c r="Q16" t="s">
+        <v>163</v>
+      </c>
       <c r="R16" s="37"/>
     </row>
-    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5"/>
       <c r="B17" s="118">
         <f t="shared" si="6"/>
@@ -3686,7 +3751,7 @@
       </c>
       <c r="R17" s="37"/>
     </row>
-    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5"/>
       <c r="B18" s="118">
         <f t="shared" si="6"/>
@@ -3741,7 +3806,7 @@
       </c>
       <c r="R18" s="37"/>
     </row>
-    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5"/>
       <c r="B19" s="118">
         <f t="shared" si="6"/>
@@ -3800,7 +3865,7 @@
       </c>
       <c r="R19" s="37"/>
     </row>
-    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5"/>
       <c r="B20" s="118">
         <f t="shared" si="6"/>
@@ -3859,7 +3924,7 @@
       </c>
       <c r="R20" s="37"/>
     </row>
-    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
       <c r="B21" s="118">
         <f t="shared" si="6"/>
@@ -3914,16 +3979,16 @@
       </c>
       <c r="R21" s="37"/>
     </row>
-    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="118">
+    <row r="22" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="225"/>
+      <c r="B22" s="224">
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="224" t="s">
         <v>121</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D22" s="224" t="s">
         <v>90</v>
       </c>
       <c r="E22" s="51">
@@ -3972,7 +4037,7 @@
       </c>
       <c r="R22" s="37"/>
     </row>
-    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
@@ -4028,7 +4093,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>15</v>
       </c>
@@ -4086,7 +4151,7 @@
       <c r="Q24" s="105"/>
       <c r="R24" s="104"/>
     </row>
-    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>16</v>
       </c>
@@ -4142,7 +4207,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>16</v>
       </c>
@@ -4198,7 +4263,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>17</v>
       </c>
@@ -4254,7 +4319,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>17</v>
       </c>
@@ -4314,7 +4379,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>18</v>
       </c>
@@ -4371,7 +4436,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>18</v>
       </c>
@@ -4427,7 +4492,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>19</v>
       </c>
@@ -4483,7 +4548,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="s">
         <v>19</v>
       </c>
@@ -4539,7 +4604,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>20</v>
       </c>
@@ -4597,7 +4662,7 @@
       </c>
       <c r="R33" s="36"/>
     </row>
-    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>20</v>
       </c>
@@ -4656,7 +4721,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>21</v>
       </c>
@@ -4713,7 +4778,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
         <v>21</v>
       </c>
@@ -4770,7 +4835,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
         <v>22</v>
       </c>
@@ -4830,7 +4895,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
         <v>23</v>
       </c>
@@ -4890,7 +4955,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="s">
         <v>24</v>
       </c>
@@ -4950,7 +5015,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
         <v>25</v>
       </c>
@@ -5010,7 +5075,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
         <v>27</v>
       </c>
@@ -5070,7 +5135,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
         <v>27</v>
       </c>
@@ -5130,7 +5195,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
         <v>27</v>
       </c>
@@ -5188,7 +5253,7 @@
       </c>
       <c r="Q43" s="104"/>
     </row>
-    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>27</v>
       </c>
@@ -5199,7 +5264,7 @@
       <c r="C44" s="48">
         <v>3301</v>
       </c>
-      <c r="D44" s="140" t="s">
+      <c r="D44" s="138" t="s">
         <v>127</v>
       </c>
       <c r="E44" s="51">
@@ -5244,7 +5309,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
         <v>27</v>
       </c>
@@ -5301,8 +5366,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="137"/>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B46" s="118">
         <f t="shared" ref="B46:B64" si="8">B45+1</f>
         <v>40</v>
@@ -5356,16 +5420,15 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="137"/>
-      <c r="B47" s="118">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B47" s="157">
         <f t="shared" si="8"/>
         <v>41</v>
       </c>
-      <c r="C47" s="48">
+      <c r="C47" s="157">
         <v>3304</v>
       </c>
-      <c r="D47" s="48" t="s">
+      <c r="D47" s="157" t="s">
         <v>148</v>
       </c>
       <c r="E47" s="51">
@@ -5410,8 +5473,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="137"/>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B48" s="118">
         <f t="shared" si="8"/>
         <v>42</v>
@@ -5464,8 +5526,7 @@
         <v>0.42000000000000021</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="137"/>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B49" s="118">
         <f t="shared" si="8"/>
         <v>43</v>
@@ -5519,8 +5580,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="137"/>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B50" s="118">
         <f t="shared" si="8"/>
         <v>44</v>
@@ -5574,8 +5634,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="137"/>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B51" s="118">
         <f t="shared" si="8"/>
         <v>45</v>
@@ -5628,8 +5687,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="137"/>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B52" s="118">
         <f t="shared" si="8"/>
         <v>46</v>
@@ -5682,8 +5740,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="137"/>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B53" s="118">
         <f t="shared" si="8"/>
         <v>47</v>
@@ -5736,8 +5793,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="137"/>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B54" s="118">
         <f t="shared" si="8"/>
         <v>48</v>
@@ -5794,8 +5850,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="137"/>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B55" s="118">
         <f t="shared" si="8"/>
         <v>49</v>
@@ -5852,8 +5907,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="137"/>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B56" s="118">
         <f t="shared" si="8"/>
         <v>50</v>
@@ -5910,8 +5964,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="137"/>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B57" s="118">
         <f t="shared" si="8"/>
         <v>51</v>
@@ -5965,8 +6018,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="137"/>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B58" s="118">
         <f t="shared" si="8"/>
         <v>52</v>
@@ -6019,8 +6071,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="137"/>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B59" s="118">
         <f t="shared" si="8"/>
         <v>53</v>
@@ -6073,8 +6124,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="137"/>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B60" s="118">
         <f t="shared" si="8"/>
         <v>54</v>
@@ -6127,8 +6177,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="137"/>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B61" s="118">
         <f t="shared" si="8"/>
         <v>55</v>
@@ -6181,8 +6230,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="137"/>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B62" s="118">
         <f t="shared" si="8"/>
         <v>56</v>
@@ -6236,8 +6284,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="137"/>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B63" s="118">
         <f t="shared" si="8"/>
         <v>57</v>
@@ -6290,8 +6337,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="137"/>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B64" s="118">
         <f t="shared" si="8"/>
         <v>58</v>
@@ -6344,8 +6390,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A65" s="137"/>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="118"/>
       <c r="C65" s="48"/>
       <c r="D65" s="48"/>
@@ -6362,11 +6407,11 @@
       <c r="O65" s="52"/>
       <c r="P65" s="37"/>
     </row>
-    <row r="66" spans="1:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="64"/>
       <c r="C66" s="65"/>
-      <c r="D66" s="138"/>
-      <c r="E66" s="141">
+      <c r="D66" s="136"/>
+      <c r="E66" s="139">
         <f>SUM(E6:E64)</f>
         <v>99.940000000000026</v>
       </c>
@@ -6378,7 +6423,7 @@
         <f>SUM(G6:G64)</f>
         <v>2804769.5600000005</v>
       </c>
-      <c r="H66" s="139">
+      <c r="H66" s="137">
         <f t="shared" ref="H66" si="9">SUM(H6:H45)</f>
         <v>0</v>
       </c>
@@ -6411,92 +6456,97 @@
         <v>26173832.109999999</v>
       </c>
     </row>
-    <row r="67" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D67" s="41"/>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:16" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D69" s="177" t="s">
+    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="69" spans="2:16" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D69" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="E69" s="177"/>
-      <c r="F69" s="177"/>
-      <c r="G69" s="177"/>
-      <c r="H69" s="177"/>
-      <c r="I69" s="177"/>
-      <c r="J69" s="177"/>
-      <c r="K69" s="177"/>
-      <c r="L69" s="177"/>
-      <c r="M69" s="177"/>
-      <c r="N69" s="177"/>
-    </row>
-    <row r="70" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D70" s="177"/>
-      <c r="E70" s="177"/>
-      <c r="F70" s="177"/>
-      <c r="G70" s="177"/>
-      <c r="H70" s="177"/>
-      <c r="I70" s="177"/>
-      <c r="J70" s="177"/>
-      <c r="K70" s="177"/>
-      <c r="L70" s="177"/>
-      <c r="M70" s="177"/>
-      <c r="N70" s="177"/>
-    </row>
-    <row r="71" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D71" s="177"/>
-      <c r="E71" s="177"/>
-      <c r="F71" s="177"/>
-      <c r="G71" s="177"/>
-      <c r="H71" s="177"/>
-      <c r="I71" s="177"/>
-      <c r="J71" s="177"/>
-      <c r="K71" s="177"/>
-      <c r="L71" s="177"/>
-      <c r="M71" s="177"/>
-      <c r="N71" s="177"/>
-    </row>
-    <row r="72" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D72" s="177"/>
-      <c r="E72" s="177"/>
-      <c r="F72" s="177"/>
-      <c r="G72" s="177"/>
-      <c r="H72" s="177"/>
-      <c r="I72" s="177"/>
-      <c r="J72" s="177"/>
-      <c r="K72" s="177"/>
-      <c r="L72" s="177"/>
-      <c r="M72" s="177"/>
-      <c r="N72" s="177"/>
-    </row>
-    <row r="73" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D73" s="177"/>
-      <c r="E73" s="177"/>
-      <c r="F73" s="177"/>
-      <c r="G73" s="177"/>
-      <c r="H73" s="177"/>
-      <c r="I73" s="177"/>
-      <c r="J73" s="177"/>
-      <c r="K73" s="177"/>
-      <c r="L73" s="177"/>
-      <c r="M73" s="177"/>
-      <c r="N73" s="177"/>
-    </row>
-    <row r="74" spans="1:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D74" s="177"/>
-      <c r="E74" s="177"/>
-      <c r="F74" s="177"/>
-      <c r="G74" s="177"/>
-      <c r="H74" s="177"/>
-      <c r="I74" s="177"/>
-      <c r="J74" s="177"/>
-      <c r="K74" s="177"/>
-      <c r="L74" s="177"/>
-      <c r="M74" s="177"/>
-      <c r="N74" s="177"/>
+      <c r="E69" s="184"/>
+      <c r="F69" s="184"/>
+      <c r="G69" s="184"/>
+      <c r="H69" s="184"/>
+      <c r="I69" s="184"/>
+      <c r="J69" s="184"/>
+      <c r="K69" s="184"/>
+      <c r="L69" s="184"/>
+      <c r="M69" s="184"/>
+      <c r="N69" s="184"/>
+    </row>
+    <row r="70" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D70" s="184"/>
+      <c r="E70" s="184"/>
+      <c r="F70" s="184"/>
+      <c r="G70" s="184"/>
+      <c r="H70" s="184"/>
+      <c r="I70" s="184"/>
+      <c r="J70" s="184"/>
+      <c r="K70" s="184"/>
+      <c r="L70" s="184"/>
+      <c r="M70" s="184"/>
+      <c r="N70" s="184"/>
+    </row>
+    <row r="71" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="184"/>
+      <c r="E71" s="184"/>
+      <c r="F71" s="184"/>
+      <c r="G71" s="184"/>
+      <c r="H71" s="184"/>
+      <c r="I71" s="184"/>
+      <c r="J71" s="184"/>
+      <c r="K71" s="184"/>
+      <c r="L71" s="184"/>
+      <c r="M71" s="184"/>
+      <c r="N71" s="184"/>
+    </row>
+    <row r="72" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="184"/>
+      <c r="E72" s="184"/>
+      <c r="F72" s="184"/>
+      <c r="G72" s="184"/>
+      <c r="H72" s="184"/>
+      <c r="I72" s="184"/>
+      <c r="J72" s="184"/>
+      <c r="K72" s="184"/>
+      <c r="L72" s="184"/>
+      <c r="M72" s="184"/>
+      <c r="N72" s="184"/>
+    </row>
+    <row r="73" spans="2:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="184"/>
+      <c r="E73" s="184"/>
+      <c r="F73" s="184"/>
+      <c r="G73" s="184"/>
+      <c r="H73" s="184"/>
+      <c r="I73" s="184"/>
+      <c r="J73" s="184"/>
+      <c r="K73" s="184"/>
+      <c r="L73" s="184"/>
+      <c r="M73" s="184"/>
+      <c r="N73" s="184"/>
+    </row>
+    <row r="74" spans="2:16" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="184"/>
+      <c r="E74" s="184"/>
+      <c r="F74" s="184"/>
+      <c r="G74" s="184"/>
+      <c r="H74" s="184"/>
+      <c r="I74" s="184"/>
+      <c r="J74" s="184"/>
+      <c r="K74" s="184"/>
+      <c r="L74" s="184"/>
+      <c r="M74" s="184"/>
+      <c r="N74" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="B1:J2"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="D69:N74"/>
@@ -6509,11 +6559,6 @@
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="B3:O3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6522,9 +6567,184 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B56D240-6D8B-4144-A545-69291A6FAA07}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="C2:H24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="2" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C3" s="153" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="154">
+        <v>1</v>
+      </c>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="151"/>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C4" s="155" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="156">
+        <v>9</v>
+      </c>
+      <c r="H4" s="152"/>
+    </row>
+    <row r="5" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="155"/>
+      <c r="D5" s="156"/>
+      <c r="H5" s="152"/>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="202" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="203"/>
+      <c r="E6" s="203"/>
+      <c r="F6" s="203"/>
+      <c r="G6" s="203"/>
+      <c r="H6" s="204"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="205"/>
+      <c r="D7" s="206"/>
+      <c r="E7" s="206"/>
+      <c r="F7" s="206"/>
+      <c r="G7" s="206"/>
+      <c r="H7" s="207"/>
+    </row>
+    <row r="8" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="208"/>
+      <c r="D8" s="209"/>
+      <c r="E8" s="209"/>
+      <c r="F8" s="209"/>
+      <c r="G8" s="209"/>
+      <c r="H8" s="210"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="104"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+    </row>
+    <row r="10" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="104"/>
+      <c r="D10" s="104"/>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="159" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="160">
+        <f>D3+1</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="150"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="150"/>
+      <c r="H11" s="151"/>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="161" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="158">
+        <v>41</v>
+      </c>
+      <c r="H12" s="152"/>
+    </row>
+    <row r="13" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="161"/>
+      <c r="D13" s="158"/>
+      <c r="H13" s="152"/>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="202" t="s">
+        <v>181</v>
+      </c>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="204"/>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="205"/>
+      <c r="D15" s="206"/>
+      <c r="E15" s="206"/>
+      <c r="F15" s="206"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="207"/>
+    </row>
+    <row r="16" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="208"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="209"/>
+      <c r="G16" s="209"/>
+      <c r="H16" s="210"/>
+    </row>
+    <row r="18" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="211" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="212">
+        <f>D11+1</f>
+        <v>3</v>
+      </c>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="151"/>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="213" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="214" t="s">
+        <v>182</v>
+      </c>
+      <c r="H20" s="152"/>
+    </row>
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="213"/>
+      <c r="D21" s="214"/>
+      <c r="H21" s="152"/>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C22" s="215" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="216"/>
+      <c r="E22" s="216"/>
+      <c r="F22" s="216"/>
+      <c r="G22" s="216"/>
+      <c r="H22" s="217"/>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="218"/>
+      <c r="D23" s="219"/>
+      <c r="E23" s="219"/>
+      <c r="F23" s="219"/>
+      <c r="G23" s="219"/>
+      <c r="H23" s="220"/>
+    </row>
+    <row r="24" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C24" s="221"/>
+      <c r="D24" s="222"/>
+      <c r="E24" s="222"/>
+      <c r="F24" s="222"/>
+      <c r="G24" s="222"/>
+      <c r="H24" s="223"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C6:H8"/>
+    <mergeCell ref="C14:H16"/>
+    <mergeCell ref="C22:H24"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>